--- a/recommendations/latest.xlsx
+++ b/recommendations/latest.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommendations" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recommendations'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recommendations'!$A$1:$H$170</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,15 +28,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -56,8 +65,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -424,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -479,8 +491,6601 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Data Scientist, GTM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>New York City, NY; San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5196852008</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Clay</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Growth Strategist, Enterprise (Customer Success)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/claylabs/c605042d-1bd4-4e0d-aa82-d92a2abecb59</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Clay</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>GTME Ecosystem - GTME &amp; AI Teacher</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/claylabs/1b1c004f-0e6a-41b6-bac3-971448b63a07</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Clay</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Manager, Enterprise Growth (Customer Success)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/claylabs/f8e696cf-55b8-4c0e-80d3-2c03abaa09a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cresta</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Forward Deployed Product Manager - AI Agent (EMEA)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>United Kingdom (Remote)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/cresta/jobs/5068157008</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Senior Product Manager, Enterprise Platform</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Denver, Colorado, United States, AMER</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://www.fivetran.com/careers/job?gh_jid=7547715003</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Senior Product Manager, Enterprise Platform</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Oakland, California, United States, AMER</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.fivetran.com/careers/job?gh_jid=7535819003</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>GTM Technology Product Owner — Growth</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/harvey/26954747-1019-405f-a6b7-ff454517924f</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>GTM Technology Product Owner — Growth</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/harvey/4ebfa721-ab27-44fb-8359-6daaede4b43e</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sigma Computing</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Product Manager, AI Platform &amp; Performance </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/sigmacomputing/jobs/7767898003</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Amazon GTM Partnership, Startups</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY | Seattle, WA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5215052008</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager, API Growth</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY | Seattle, WA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5181852008</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager, Compute Platform</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY | Seattle, WA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5124623008</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager, GTM Experiences</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5254623008</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager, Multi-Cloud Growth - Google</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5153924008</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager, API Platform</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | Seattle, WA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5256303008</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager, Apps Platform</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | Seattle, WA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5251609008</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager, Data Center Infrastructure</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY | Seattle, WA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5013743008</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager, Databases</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | Seattle, WA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5251612008</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Clay</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Forward Deployed GTME</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/claylabs/26c9a251-b616-49f7-a489-4d393a02ea5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Clay</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Growth Strategist, Scale (Customer Success)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/claylabs/55694518-a6ac-4f46-8ec8-ffbf8ab39917</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Clay</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>GTM Engineer - CX</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/claylabs/e43101dd-4e98-4c60-bc1b-adbbb38c7b15</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Clay</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>GTM Engineer - Ecosystem</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/claylabs/242be863-2f62-44a7-909d-6c351dee81d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Clay</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>GTM Engineer - Seller Efficiency</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/claylabs/d5c7f612-10e7-4080-8b8a-d51e70fff9c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Clay</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>GTM Engineer - Systems and Infrastructure</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/claylabs/f90028b7-6c35-4392-824c-105967ccd406</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Clay</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>GTM Ops Manager, Quote to Cash</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/claylabs/0a88196b-f7ab-4340-84fa-ecf80b45705b</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Clay</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>GTME Ecosystem - Certifications &amp; Badges Lead</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/claylabs/006b295b-8f2c-4bca-9d6b-aa54be6df972</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Clay</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>GTME Ecosystem - Create Your Own Role</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/claylabs/45fbd224-6a30-4b8e-8938-139ae0a0127f</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Clay</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>GTME Ecosystem - GTME University Lead</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/claylabs/0532ee84-60a2-4998-a461-eabc555ee4c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Clay</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Head of GTM Architecture</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/claylabs/0df88e24-28da-4376-956d-926111832a32</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Clay</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Product Marketing, GTM</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/claylabs/6579de6f-b5df-46df-bb73-e8d82955f293</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Cohere</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>RevOps - Compensation &amp; GTM Integration</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/cohere/f3cf5d6a-5a93-41b5-8a00-160e120859ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Cresta</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>GTM Engineer</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>United States (Remote)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/cresta/jobs/5123589008</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Cresta</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Platform Product Manager</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>United States (Remote)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/cresta/jobs/5114374008</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Decagon</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GTM Enablement Manager </t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/decagon/0e8a35cd-be75-436e-8407-f4e8dd2d2c59</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Decagon</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Senior Agent Product Manager - Germany</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/decagon/4ef4e97e-43b3-420f-be6f-1d0aab181149</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Decagon</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Senior Agent Product Manager - Sydney</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/decagon/7d9e30a4-249b-4032-930c-4bd7bc8addb1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Director, GTM Strategy &amp; Planning</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Denver, Colorado, United States, AMER</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.fivetran.com/careers/job?gh_jid=7785999003</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Senior Product Manager, Growth</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Oakland, California, United States, AMER</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.fivetran.com/careers/job?gh_jid=7735422003</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Glean</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>GTM Strategic Finance Manager</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gleanwork/jobs/4674234005</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Glean</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager, Agent Security &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gleanwork/jobs/4694761005</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Glean</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager, Agent Security &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Mountain View, CA</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gleanwork/jobs/4525297005</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Glean</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager, AI Quality</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Mountain View, CA</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gleanwork/jobs/4694764005</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Glean</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager, AI Quality</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gleanwork/jobs/4525518005</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Glean</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager, API Platform</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Mountain View, CA</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gleanwork/jobs/4710996005</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Glean</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager, Enterprise Intelligence</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Mountain View, CA</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gleanwork/jobs/4702369005</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Glean</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager, Growth</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gleanwork/jobs/4702151005</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Glean</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager, Growth</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Mountain View, CA</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gleanwork/jobs/4702367005</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/harvey/0d750bf9-d3f2-4816-9e28-23d12a0ef2e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>GTM Strategic Finance Lead</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/harvey/99c7e2f7-9fe9-4373-9bf3-5470044bcd77</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>GTM Strategic Finance Lead</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/harvey/d5d27b01-b6d7-4e34-976d-9d04b334afdc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>GTM Technology Product Owner</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/harvey/320427e4-333f-445c-87f1-67d08ab0fa6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>GTM Technology Product Owner</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/harvey/8ae1a13f-362b-4e7f-8456-c0fbe5d33571</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>GTM Technology Product Owner</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/harvey/9bdec908-b2b7-44b0-8695-582bed7cf9ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>1</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Head of Customer Success, Enterprise</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/harvey/88095128-3c1c-48c1-b37b-68e1349d9834</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Head of Customer Success, Enterprise</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/harvey/8ae3a90d-ebf8-4202-96d3-9f74c2737cd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>1</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Staff Product Manager, Legal Operations Platform</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/harvey/4221e6ce-fb4f-4f20-a615-aa1b85d2ef3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>1</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Staff Product Manager, Legal Operations Platform</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/harvey/d1b7c79c-e61b-4e68-a690-89a008f03670</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>1</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager, Platform &amp; Infrastructure</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/harvey/467049ce-b5ea-4063-95aa-71c9742768d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>1</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Parloa</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>GTM Engineer</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Remotely in the USA</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/parloa/jobs/4843556101</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>1</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Perplexity</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/perplexity/9a570310-305d-4f4e-9807-b8862b31194b</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>1</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Perplexity</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Scaled Enterprise Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/perplexity/fdc2ea75-c198-4a9e-9c0a-df835ed61ed0</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>1</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Sana</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>GTM Associate</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/sana-roles/bbdcb76a-9662-484a-85b4-5b243ef7e1f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>1</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>GTM Engineer</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/sierra/1c991675-099f-49dd-9b9b-bd3c9111e65c</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>1</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>GTM Operations, Planning</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/sierra/b6d4c3fe-5ca9-46f9-ba56-fbb190574886</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>1</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>GTM Strategy and Operations</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/sierra/6b9b6904-a4b1-444b-8c35-f2bbb5ee2ff5</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>1</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager, Agent Development</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/sierra/effd7cd2-8a28-4bae-a3b8-40720ba09717</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>1</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager, Agent Development (Brazilian Portuguese speaking)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/sierra/4f0e65ba-b262-4d79-b926-3988f8eb0c00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>1</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager, Agent Development - Flagship Deployment</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/sierra/758beaca-db59-4e46-9867-7a93989735a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>1</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager, Agent Development - Healthcare</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/sierra/65eb2c63-c936-4e8e-87e7-ea080dcdca73</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>1</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager, Agent SDK</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/sierra/10d2e2f1-6657-40c9-b6fb-6999c76df6cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>1</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Sigma Computing</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Director of Product Marketing, AI</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/sigmacomputing/jobs/7784475003</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>1</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Sigma Computing</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Customer Success Manager - Upper Midwest Region</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/sigmacomputing/jobs/7787045003</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>0</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Product Manager, Safeguards Rare Harms</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5139628008</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>0</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Beneficial Deployments Customer Success Manager, Scaled Partnerships </t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5225812008</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>0</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Community &amp; Executive Escalations Program Manager</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5207565008</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>0</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Customer Program Manager, Executive Briefing Center</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5251699008</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>0</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Customer Success Manager, Beneficial Deployments - Global Development</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5262637008</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>0</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Customer Success Manager, Digital Native Business</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5062733008</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>0</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Customer Success Manager, Higher Education</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5175932008</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>0</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Customer Success Manager, Industries</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>New York City, NY</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5068570008</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>0</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Customer Success Manager, Public Sector</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>New York City, NY; San Francisco, CA; Washington, DC</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5262369008</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>0</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Customer Success Manager, Scaled</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>New York City, NY; San Francisco, CA; Seattle, WA</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5174700008</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>0</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Customer Success Manager, Strategics</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>New York City, NY; San Francisco, CA; Seattle, WA</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5082455008</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>0</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Customer Success Programs Manager</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Boston, MA; New York City, NY; San Francisco, CA; Seattle, WA; Washington, DC</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5226954008</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>0</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Global Senior Equity Program Manager</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | Seattle, WA</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5162711008</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>0</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Head of Programmatic Customer Success</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | Seattle, WA | New York City, NY | Washington, DC</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5153580008</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>0</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Legal Program Manager, Compute &amp; Infrastructure</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | Seattle, WA</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5274117008</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>0</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Product Engineer, Computer Use </t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY | Seattle, WA</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5238637008</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>0</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Product Manager, Claude Code Model Performance </t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | Seattle, WA</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5247640008</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>0</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager, Developer Productivity</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5220143008</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>0</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Research Product Manager, Model Behaviors</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5247407008</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>0</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager, Cloud Inference</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5201264008</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>0</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Technical Program Manager, Compute </t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY | Seattle, WA</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5138044008</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>0</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager, Inference Performance</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | Seattle, WA</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5107763008</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>0</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager, Infrastructure</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY | Seattle, WA</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5111783008</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>0</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Technical Program Manager, Launches  </t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5208193008</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>0</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager, Research</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5203545008</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>0</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager, Safeguards (Infrastructure &amp; Evals)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY | Seattle, WA</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5108695008</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>0</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager, Security</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY | Seattle, WA</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/4989788008</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>0</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Web Product Manager</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5281348008</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>0</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Clay</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>ClayDR Enablement Program Manager</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/claylabs/13af486b-f105-443f-94f2-29206afb9a77</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>0</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Clay</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Technical Enablement Program Manager</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/claylabs/494dd605-64a7-4647-bf86-cb1034f2327c</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>0</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Cohere</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager, Safety Research</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/cohere/a8122632-cc3b-4a1a-bd78-4b4b9466cb38</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>0</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Cohere</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager, Product Engineering</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/cohere/f00dbf81-17ff-4584-b015-67dfae1dc59c</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>0</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Cresta</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Associate Forward Deployed Product Manager</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>United States, Remote</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/cresta/jobs/4992510008</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>0</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Cresta</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Senior Product Engineer, Cresta Labs</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>United States (Remote)</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/cresta/jobs/5288477008</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>0</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Decagon</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/decagon/d790a2a2-958d-4f49-96ed-adbd68d2e6ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>0</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Decagon</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager, Duet</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/decagon/9109be1c-b6e3-430f-a964-887253ef891a</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>0</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Decagon</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager, Research</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/decagon/6321ea2f-4e21-4c18-8859-b4ef5489b6fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>0</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Decagon</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/decagon/d32da775-c5ea-420d-a07e-13412044c27b</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>0</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Denver, Colorado, United States, AMER</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://www.fivetran.com/careers/job?gh_jid=7773958003</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>0</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager - Fusion</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Remote, Colorado, United States, AMER</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>https://www.fivetran.com/careers/job?gh_jid=7787885003</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>0</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Product Manager - Integrations </t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Denver, Colorado, United States, AMER</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>https://www.fivetran.com/careers/job?gh_jid=7786318003</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>0</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Product Manager - Integrations </t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Oakland, California, United States</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>https://www.fivetran.com/careers/job?gh_jid=7559181003</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>0</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Senior Product Manager, Observability &amp; Monitoring</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Oakland, California, United States, AMER</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>https://www.fivetran.com/careers/job?gh_jid=6645141003</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>0</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Senior Product Manager, Observability &amp; Monitoring</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Denver, Colorado, United States, AMER</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>https://www.fivetran.com/careers/job?gh_jid=6648548003</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>0</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Senior Staff Program Manager</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Oakland, California, United States, AMER</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>https://www.fivetran.com/careers/job?gh_jid=7620909003</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>0</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Staff Product Manager- Developer Experience</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Oakland, California, United States</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>https://www.fivetran.com/careers/job?gh_jid=7790909003</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>0</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Staff Technical Product Manager, Quote to Order</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Oakland, California, United States, AMER</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>https://www.fivetran.com/careers/job?gh_jid=7758876003</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>0</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Glean</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Product Management Lead, Core Experience</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Mountain View, CA</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gleanwork/jobs/4559476005</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>0</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Glean</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Mountain View, CA</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gleanwork/jobs/4007711005</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>0</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Glean</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager, Connectors</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Mountain View, CA</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gleanwork/jobs/4701618005</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>0</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Glean</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager, Core Experience</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gleanwork/jobs/4702147005</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>0</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Glean</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager, Core Experience</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Mountain View, CA</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gleanwork/jobs/4702368005</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>0</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Head of Product Operations</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/harvey/cf370c84-a157-4ecb-ae57-9a84953e0d96</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>0</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Head of Product Operations</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/harvey/e646ca56-2122-4309-b2bb-0be7f26d42cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>0</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Innovation Product Manager</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/harvey/e5272fbe-4431-4841-bf00-b9f59812b82a</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>0</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Mid-Market Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/harvey/c2e8772a-ca9c-44ee-95fb-bbd64f57e7c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>0</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Mid-Market Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/harvey/dcacb8c5-d91b-4f8f-a444-d8c86cb606c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>0</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Program Manager, Customer Engagement &amp; Community</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/harvey/641764cf-2907-41e5-b36d-797b33b8f1a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>0</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Program Manager, Customer Engagement &amp; Community</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/harvey/e9fc1fbe-0aca-403f-b442-9b5b52fca8a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>0</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Staff Product Manager</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/harvey/8d092528-2554-42e4-a68b-67307b48e6aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>0</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Staff Product Manager, New Products</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/harvey/e89103ca-765f-42f1-882a-80364f3c2321</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>0</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Staff Product Manager, New Verticals</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/harvey/2cbe13b9-a44b-47d3-abb8-45d9a98b05f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>0</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager, Incident Response</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/harvey/36bce60d-eedc-4347-af80-9321aaa88b48</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>0</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager, Incident Response</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/harvey/76d7a078-01c9-48d1-8481-3bfb728b657e</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>0</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager, Product Trust</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/harvey/49ffdd0c-ed1d-4965-aa60-b5bd8c128aae</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>0</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager, Quality and Reliability</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/harvey/9ea6dcda-7869-4181-b493-2822bbc14097</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>0</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Hightouch</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Full Stack Product Engineer</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Remote (North America)</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/hightouch/jobs/4620430004</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>0</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Hightouch</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Customer Success Engineer</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Remote (North America)</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/hightouch/jobs/5699984004</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>0</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Hightouch</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Go-to-Market Engineer</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Remote, United States</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/hightouch/jobs/5823552004</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>0</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Mistral</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager, Cloud Partnerships</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/mistral/ca22a1ac-c87e-4463-914a-6753ca79318c</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>0</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Nuro</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Head of Product</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Mountain View, California (HQ)</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>https://nuro.ai/careersitem?gh_jid=8044828</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>0</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Nuro</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>People &amp; Talent Program Manager</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Mountain View, California (HQ)</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>https://nuro.ai/careersitem?gh_jid=7977114</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>0</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Nuro</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Senior Program Manager, Eval Operations</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Mountain View, California (HQ)</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>https://nuro.ai/careersitem?gh_jid=7838576</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>0</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Nuro</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Senior Program Manager, Mapping Operations</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Mountain View, California (HQ)</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>https://nuro.ai/careersitem?gh_jid=7968169</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>0</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Nuro</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Senior/Staff Software Technical Program Manager, Systems Engineering</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Mountain View, California (HQ)</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>https://nuro.ai/careersitem?gh_jid=6114642</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>0</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Nuro</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Staff Program Manager, Office of the CEO</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Mountain View, California (HQ)</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>https://nuro.ai/careersitem?gh_jid=7863426</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>0</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Parloa</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Sr Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>New York Office</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/parloa/jobs/4877821101</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>0</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Parloa</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>New York Office</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/parloa/jobs/4877824101</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>0</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Parloa</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager (Germany)</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Berlin Office; Remotely in Germany</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/parloa/jobs/4719998101</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>0</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Perplexity</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager (Builder)</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/perplexity/f25e190e-0508-4707-b575-fcaed358dc13</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>0</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Localization Program Manager</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/sierra/4041855f-5a09-47ea-80d3-3141454655f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>0</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager, Ghostwriter</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/sierra/22ba107d-de01-4aa3-98fc-838cccad760c</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>0</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager, Infrastructure</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/sierra/1e052261-0c89-4ccb-abfa-3820a1596a6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>0</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager, Voice</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/sierra/0c66e8ed-1c18-4b64-ad27-a522a866b6e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>0</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Security Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/sierra/53a8fd83-3e58-41a4-b014-2da447db820b</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>0</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Sigma Computing</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer Success Architect </t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/sigmacomputing/jobs/7598665003</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>0</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Sigma Computing</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Digital Customer Success Manager </t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>San Francisco, New York</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/sigmacomputing/jobs/7776910003</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>0</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Sourcegraph</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Senior Customer Success Manager - US East [IC3]</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/sourcegraph91/jobs/5989776004</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>Product Manager, Agent Data Platform</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/sierra/422cb7bb-ab03-447b-808c-6d72f59bbd2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>Product Management, Human Data Platform</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5195866008</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>Cresta</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>Forward Deployed Product Manager, AI Agent</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>United States (Remote)</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G165" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/cresta/jobs/4738837008</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>Decagon</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>Senior Agent Product Manager</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G166" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/decagon/dcf9b561-f2fb-422b-88a9-33ce76e96608</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>Decagon</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>Senior Agent Product Manager</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/decagon/e31c0645-7325-43b9-9d58-0acc40904240</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>Glean</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>Product Manager, Enterprise Intelligence</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F168" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G168" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gleanwork/jobs/4701912005</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>Hightouch</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>Lead Product Manager, Agentic Personalization</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>SF, NY, Remote</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F169" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G169" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/hightouch/jobs/5834919004</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>Product Manager, Agent Studio</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F170" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G170" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/sierra/5aaa2eeb-92bc-4b0a-901e-8e091eff819e</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:H170"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId169"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>